--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 87억(1.9%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 18종목  /  매도 24종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 43억(1.0%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 18종목  /  매도 24종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1163,111 +1163,111 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-202901400</v>
+        <v>-1446412500</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>3.66%→3.63%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>156→143</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>436873500</v>
+        <v>4636800000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>5.67%→7.11%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1446412500</v>
+        <v>-202901400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.63%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>156→143</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4636800000</v>
+        <v>436873500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>5.67%→7.11%</t>
+          <t>0.33%→0.40%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1242000000</v>
+        <v>-273861000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.54%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→65</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-444015000</v>
+        <v>-1242000000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>1.97%→1.54%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>77→65</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-273861000</v>
+        <v>-444015000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1511,23 +1511,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1314450000</v>
+        <v>-429007500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.21%→3.00%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1539,23 +1539,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-429007500</v>
+        <v>-1314450000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.21%→3.00%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 39억(1.0%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 19억(0.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1965,920 +1965,1644 @@
       <c r="K40" s="17" t="n"/>
     </row>
     <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
-      <c r="J42" s="19" t="n"/>
-      <c r="K42" s="19" t="n"/>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="19" t="n"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="19" t="n"/>
-      <c r="K44" s="19" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 1억(0.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 75억(2.9%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>1223025000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>1.27%→1.72%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>250→350</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>한국피아이엠</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-1756122100</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>1.31%→0.50%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>80→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>1291798000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>0.09%→0.62%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>20→120</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-1163114500</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→4.69%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>375→341</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>메쥬</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>452802850</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>0.08%→0.26%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>24→77</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-216230820</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.44%→0.30%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>150→116</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>1295697500</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>0.82%→1.44%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>30→47</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋벤처투자</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-298134500</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.14%→0.91%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>250→221</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-786990000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>1.35%→0.95%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>20→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-597687000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>5.13%→5.05%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>110→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 57억(2.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>코미코  (신규)</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>395</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>1590112000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→5.45%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-56</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-160787200</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>8.12%→7.12%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>780→724</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>67900920</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>0.15%→0.38%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>51→133</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>새로닉스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-43</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-35511120</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>2.84%→2.57%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>950→907</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>코스맥스엔비티</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>41869200</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>0.27%→0.40%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>122→191</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>덕산하이메탈</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-24505840</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>0.59%→0.48%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>227→193</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>33690720</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.38%→1.42%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>474→516</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-81607200</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>0.95%→0.62%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>77→53</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>71228700</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>3.07%→3.14%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>321→348</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-56832000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>1.56%→1.28%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>121→105</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>116727600</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.40%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>0→22</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-47049200</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>0.46%→0.28%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>30→19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>21725660</v>
+        <v>5655028500</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>3.15%→3.05%</t>
+          <t>1.76%→4.46%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>680→697</t>
+          <t>200→497</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-4</v>
+        <v>-222</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-67932000</v>
+        <v>-1484309760</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.04%</t>
+          <t>2.01%→0.80%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>39→35</t>
+          <t>475→253</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>27291200</v>
+        <v>3928072000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>6.04%→5.80%</t>
+          <t>1.47%→3.34%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>977→993</t>
+          <t>151→339</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>고영  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-3</v>
+        <v>-194</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-37451400</v>
+        <v>-2085558200</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.85%→1.62%</t>
+          <t>0.90%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>41→38</t>
+          <t>194→0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>74481000</v>
+        <v>4341941700</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.59%→2.70%</t>
+          <t>13.31%→15.89%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>144→159</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="n"/>
-      <c r="H57" s="17" t="n"/>
-      <c r="I57" s="17" t="n"/>
-      <c r="J57" s="17" t="n"/>
-      <c r="K57" s="17" t="n"/>
+          <t>453→520</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-6182197600</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>3.91%→1.05%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>250→66</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>41758200</v>
+        <v>2870431200</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.08%→3.05%</t>
+          <t>2.63%→3.77%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="n"/>
-      <c r="H58" s="17" t="n"/>
-      <c r="I58" s="17" t="n"/>
-      <c r="J58" s="17" t="n"/>
-      <c r="K58" s="17" t="n"/>
+          <t>100→156</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-4212500000</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>6.47%→4.19%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>42698000</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>3.16%→3.13%</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-2199936000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>0.95%→0.00%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C60" s="11" t="n">
-        <v>7622000</v>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>2.51%→2.40%</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>363→367</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="n"/>
-      <c r="H60" s="17" t="n"/>
-      <c r="I60" s="17" t="n"/>
-      <c r="J60" s="17" t="n"/>
-      <c r="K60" s="17" t="n"/>
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-842163000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.80%→0.39%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>203→101</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>보로노이  (신규)</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>25530000</v>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.09%</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>0→2</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="n"/>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="17" t="n"/>
-      <c r="J61" s="17" t="n"/>
-      <c r="K61" s="17" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 6억(1.1%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-208276110</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.14%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>199→118</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-631335800</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.68%→0.36%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>150→82</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-398620450</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>0.57%→0.28%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-232108750</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.06%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>46→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 1억(0.2%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>878</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>1647681140</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→3.07%</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>0→878</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>한스바이오메드</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n">
-        <v>-301</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>-609281190</v>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>2.61%→1.17%</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>612→311</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>프로티나  (신규)</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>227</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>991377100</v>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.85%</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>0→227</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n">
-        <v>-230</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <v>-543020800</v>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>2.76%→1.03%</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>464→234</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>알지노믹스</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>265500900</v>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>3.57%→3.83%</t>
-        </is>
-      </c>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>498→572</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>리브스메드</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="n">
-        <v>-116</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <v>-461743800</v>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>3.38%→1.73%</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>349→233</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>1590112000</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→5.45%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>0→395</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-160787200</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>8.12%→7.12%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>780→724</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>67900920</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.15%→0.38%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>51→133</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-35511120</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>2.84%→2.57%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>41869200</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.27%→0.40%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>122→191</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-24505840</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.48%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>227→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>33690720</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>1.38%→1.42%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>474→516</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-81607200</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>0.95%→0.62%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>77→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>71228700</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>3.07%→3.14%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>321→348</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-56832000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>1.56%→1.28%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>121→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>116727600</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.40%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-47049200</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.28%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>21725660</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>3.15%→3.05%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>680→697</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-67932000</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>2.40%→2.04%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>39→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>27291200</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>6.04%→5.80%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>977→993</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-37451400</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>1.85%→1.62%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>74481000</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>2.59%→2.70%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>144→159</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n"/>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="n"/>
+      <c r="K77" s="17" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>41758200</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.08%→3.05%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n"/>
+      <c r="H78" s="17" t="n"/>
+      <c r="I78" s="17" t="n"/>
+      <c r="J78" s="17" t="n"/>
+      <c r="K78" s="17" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>42698000</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>3.16%→3.13%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>7622000</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>2.51%→2.40%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>363→367</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="n"/>
+      <c r="H80" s="17" t="n"/>
+      <c r="I80" s="17" t="n"/>
+      <c r="J80" s="17" t="n"/>
+      <c r="K80" s="17" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>보로노이  (신규)</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>25530000</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.09%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>0→2</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n"/>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>878</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>1647681140</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.07%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>0→878</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>-301</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>-609281190</v>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>2.61%→1.17%</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>612→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>991377100</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.85%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>-543020800</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→1.03%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>265500900</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>3.57%→3.83%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>-461743800</v>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>3.38%→1.73%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n">
+      <c r="B89" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C69" s="11" t="n">
+      <c r="C89" s="11" t="n">
         <v>261014600</v>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>5.63%→6.15%</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>256→278</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="H69" s="15" t="n">
+      <c r="H89" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I69" s="15" t="n">
+      <c r="I89" s="15" t="n">
         <v>-583100000</v>
       </c>
-      <c r="J69" s="16" t="inlineStr">
+      <c r="J89" s="16" t="inlineStr">
         <is>
           <t>3.60%→2.56%</t>
         </is>
       </c>
-      <c r="K69" s="13" t="inlineStr">
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="A71" s="18" t="inlineStr">
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B71" s="19" t="n"/>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-      <c r="G71" s="19" t="n"/>
-      <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
-      <c r="J71" s="19" t="n"/>
-      <c r="K71" s="19" t="n"/>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="19" t="n"/>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="19" t="n"/>
+      <c r="G91" s="19" t="n"/>
+      <c r="H91" s="19" t="n"/>
+      <c r="I91" s="19" t="n"/>
+      <c r="J91" s="19" t="n"/>
+      <c r="K91" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="G64:K64"/>
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="21">
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="G43:K43"/>
+    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="G32:K32"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A71:K71"/>
     <mergeCell ref="A42:K42"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="G84:K84"/>
+    <mergeCell ref="A67:E67"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1280191500</v>
+        <v>-2957616000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.28%</t>
+          <t>2.56%→1.67%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>74→36</t>
+          <t>132→94</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2957616000</v>
+        <v>-1280191500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.56%→1.67%</t>
+          <t>0.61%→0.28%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>132→94</t>
+          <t>74→36</t>
         </is>
       </c>
     </row>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>4636800000</v>
+        <v>436873500</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>5.67%→7.11%</t>
+          <t>0.33%→0.40%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,44 +1230,44 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>436873500</v>
+        <v>4636800000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>5.67%→7.11%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-273861000</v>
+        <v>-1242000000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.97%→1.54%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>77→65</t>
         </is>
       </c>
     </row>
@@ -1295,90 +1295,90 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1242000000</v>
+        <v>-444015000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.54%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>77→65</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>928705500</v>
+        <v>417312000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-444015000</v>
+        <v>-273861000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>417312000</v>
+        <v>928705500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1511,23 +1511,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-429007500</v>
+        <v>-1314450000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.21%→3.00%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1539,23 +1539,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1314450000</v>
+        <v>-429007500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>3.21%→3.00%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 75억(2.9%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 37억(1.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -2288,7 +2288,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 57억(2.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 28억(1.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2957616000</v>
+        <v>-1280191500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>2.56%→1.67%</t>
+          <t>0.61%→0.28%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>132→94</t>
+          <t>74→36</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1280191500</v>
+        <v>-2957616000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.28%</t>
+          <t>2.56%→1.67%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>74→36</t>
+          <t>132→94</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1242000000</v>
+        <v>-273861000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.54%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→65</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1318,67 +1318,67 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>417312000</v>
+        <v>928705500</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-273861000</v>
+        <v>-1242000000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.97%→1.54%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>77→65</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>928705500</v>
+        <v>417312000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2056,23 +2056,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1223025000</v>
+        <v>1291798000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.72%</t>
+          <t>0.09%→0.62%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>250→350</t>
+          <t>20→120</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -2100,23 +2100,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1291798000</v>
+        <v>1223025000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.62%</t>
+          <t>1.27%→1.72%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>20→120</t>
+          <t>250→350</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 43억(1.0%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 18종목  /  매도 24종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 43억(1.0%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 18종목  /  매도 24종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>12041190000</v>
+        <v>11971386000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2738661750</v>
+        <v>-2722785450</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>196</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9108414000</v>
+        <v>9055611600</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1238739750</v>
+        <v>-1231558650</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>446183325</v>
+        <v>443596755</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1239764400</v>
+        <v>-1232577360</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>72</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1848096000</v>
+        <v>1837382400</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2861775000</v>
+        <v>-2845185000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>470862900</v>
+        <v>468133260</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1280191500</v>
+        <v>-1272770100</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>443394000</v>
+        <v>440823600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-38</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2957616000</v>
+        <v>-2940470400</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>859774500</v>
+        <v>854790300</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-26</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1767987000</v>
+        <v>-1757737800</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>418057200</v>
+        <v>415633680</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-24</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-900450000</v>
+        <v>-895230000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1013472000</v>
+        <v>1007596800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-431346600</v>
+        <v>-428846040</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>848958750</v>
+        <v>844037250</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-18</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-450846000</v>
+        <v>-448232400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>391644000</v>
+        <v>389373600</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-407893500</v>
+        <v>-405528900</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1482637500</v>
+        <v>1474042500</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1163,111 +1163,111 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1446412500</v>
+        <v>-201725160</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.63%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>156→143</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>436873500</v>
+        <v>4609920000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>5.67%→7.11%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-202901400</v>
+        <v>-1438027500</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>3.66%→3.63%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>156→143</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4636800000</v>
+        <v>434340900</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>5.67%→7.11%</t>
+          <t>0.33%→0.40%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-273861000</v>
+        <v>-441441000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>875506500</v>
+        <v>870431100</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1295,46 +1295,46 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-444015000</v>
+        <v>-272273400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>928705500</v>
+        <v>414892800</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1242000000</v>
+        <v>-1234800000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1362,23 +1362,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>417312000</v>
+        <v>923321700</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-208800900</v>
+        <v>-207590460</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>380362500</v>
+        <v>378157500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>-8</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-314226000</v>
+        <v>-312404400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-885339000</v>
+        <v>-880206600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-825309000</v>
+        <v>-820524600</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1314450000</v>
+        <v>-1306830000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-429007500</v>
+        <v>-426520500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-412758000</v>
+        <v>-410365200</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1243552500</v>
+        <v>-1236343500</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 19억(0.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 19억(0.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1714,7 +1714,7 @@
         <v>564</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>4696179840</v>
+        <v>4678391280</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>-527</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-4749829920</v>
+        <v>-4731838140</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>69</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>722810880</v>
+        <v>720072960</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>-155</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1710456000</v>
+        <v>-1703977000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>50</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>727320000</v>
+        <v>724565000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>-6</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1013760000</v>
+        <v>-1009920000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>715968000</v>
+        <v>713256000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>-5</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-322344000</v>
+        <v>-321123000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>18</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>714700800</v>
+        <v>711993600</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>673358400</v>
+        <v>670807800</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>634392000</v>
+        <v>631989000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 37억(1.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 37억(1.5%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -2063,7 +2063,7 @@
         <v>100</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1291798000</v>
+        <v>1282688000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>-47</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1756122100</v>
+        <v>-1743737600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>100</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1223025000</v>
+        <v>1214400000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2121,23 +2121,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1163114500</v>
+        <v>-214705920</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.69%</t>
+          <t>0.44%→0.30%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>53</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>452802850</v>
+        <v>449609600</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-216230820</v>
+        <v>-1154912000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.30%</t>
+          <t>5.40%→4.69%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1295697500</v>
+        <v>1286560000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>-29</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-298134500</v>
+        <v>-296032000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2237,23 +2237,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-786990000</v>
+        <v>-593472000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.35%→0.95%</t>
+          <t>5.13%→5.05%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>110→105</t>
         </is>
       </c>
     </row>
@@ -2265,30 +2265,30 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-597687000</v>
+        <v>-781440000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>5.13%→5.05%</t>
+          <t>1.35%→0.95%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>110→105</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 28억(1.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 28억(1.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -2384,7 +2384,7 @@
         <v>297</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>5655028500</v>
+        <v>5621467500</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>-222</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1484309760</v>
+        <v>-1475500800</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>188</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>3928072000</v>
+        <v>3904760000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>-194</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-2085558200</v>
+        <v>-2073181000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>67</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>4341941700</v>
+        <v>4316173500</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>-184</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-6182197600</v>
+        <v>-6145508000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2870431200</v>
+        <v>2853396000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>-125</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-4212500000</v>
+        <v>-4187500000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>-102</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-2199936000</v>
+        <v>-2186880000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>-102</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-842163000</v>
+        <v>-837165000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>-81</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-208276110</v>
+        <v>-207040050</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>-68</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-631335800</v>
+        <v>-627589000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>-41</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-398620450</v>
+        <v>-396254750</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>-29</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-232108750</v>
+        <v>-230731250</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 1억(0.2%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2817,11 +2817,11 @@
         <v>395</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1590112000</v>
+        <v>809671000</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.45%</t>
+          <t>0.00%→3.03%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2838,11 +2838,11 @@
         <v>-56</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-160787200</v>
+        <v>-150220000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>8.12%→7.12%</t>
+          <t>8.07%→7.27%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2861,11 +2861,11 @@
         <v>82</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>67900920</v>
+        <v>65413040</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.15%→0.38%</t>
+          <t>0.16%→0.40%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2882,11 +2882,11 @@
         <v>-43</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-35511120</v>
+        <v>-34874720</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.57%</t>
+          <t>2.97%→2.75%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2905,11 +2905,11 @@
         <v>69</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>41869200</v>
+        <v>41154360</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.27%→0.40%</t>
+          <t>0.28%→0.43%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2926,11 +2926,11 @@
         <v>-34</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-24505840</v>
+        <v>-23524600</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.48%</t>
+          <t>0.61%→0.50%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2949,11 +2949,11 @@
         <v>42</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>33690720</v>
+        <v>30800280</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.38%→1.42%</t>
+          <t>1.34%→1.42%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -2970,11 +2970,11 @@
         <v>-24</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-81607200</v>
+        <v>-84626400</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.95%→0.62%</t>
+          <t>1.05%→0.70%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2993,11 +2993,11 @@
         <v>27</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>71228700</v>
+        <v>64135800</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>3.07%→3.14%</t>
+          <t>2.94%→3.09%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3014,11 +3014,11 @@
         <v>-16</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-56832000</v>
+        <v>-53161600</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.28%</t>
+          <t>1.55%→1.31%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -3037,11 +3037,11 @@
         <v>22</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>116727600</v>
+        <v>100936000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.40%</t>
+          <t>0.00%→0.38%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v>-11</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-47049200</v>
+        <v>-43386200</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -3081,11 +3081,11 @@
         <v>17</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>21725660</v>
+        <v>20631200</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>3.15%→3.05%</t>
+          <t>3.18%→3.17%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3102,11 +3102,11 @@
         <v>-4</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-67932000</v>
+        <v>-66748000</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.04%</t>
+          <t>2.51%→2.19%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3125,11 +3125,11 @@
         <v>16</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>27291200</v>
+        <v>24745600</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>6.04%→5.80%</t>
+          <t>5.83%→5.75%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3146,11 +3146,11 @@
         <v>-3</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-37451400</v>
+        <v>-34254600</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>1.85%→1.62%</t>
+          <t>1.81%→1.62%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3169,11 +3169,11 @@
         <v>15</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>74481000</v>
+        <v>68931000</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>2.59%→2.70%</t>
+          <t>2.55%→2.74%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3197,11 +3197,11 @@
         <v>9</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>41758200</v>
+        <v>38694600</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>3.08%→3.05%</t>
+          <t>3.04%→3.09%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3225,11 +3225,11 @@
         <v>5</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>42698000</v>
+        <v>39775000</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>3.16%→3.13%</t>
+          <t>3.13%→3.19%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -3253,11 +3253,11 @@
         <v>4</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>7622000</v>
+        <v>6941200</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>2.51%→2.40%</t>
+          <t>2.43%→2.38%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -3281,11 +3281,11 @@
         <v>2</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>25530000</v>
+        <v>22510800</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.09%</t>
+          <t>0.00%→0.08%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
@@ -3398,7 +3398,7 @@
         <v>878</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>1647681140</v>
+        <v>1619989020</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>-301</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-609281190</v>
+        <v>-599041170</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>227</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>991377100</v>
+        <v>974715300</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>-230</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-543020800</v>
+        <v>-533894400</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>74</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>265500900</v>
+        <v>261038700</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>-116</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-461743800</v>
+        <v>-453983400</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>22</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>261014600</v>
+        <v>256627800</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>-20</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-583100000</v>
+        <v>-573300000</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-441441000</v>
+        <v>-1234800000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>1.97%→1.54%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>77→65</t>
         </is>
       </c>
     </row>
@@ -1318,67 +1318,67 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>414892800</v>
+        <v>923321700</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1234800000</v>
+        <v>-441441000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.54%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>77→65</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>923321700</v>
+        <v>414892800</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1511,23 +1511,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1306830000</v>
+        <v>-426520500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.21%→3.00%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1539,23 +1539,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-426520500</v>
+        <v>-1306830000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.21%→3.00%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -2121,23 +2121,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-214705920</v>
+        <v>-1154912000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.30%</t>
+          <t>5.40%→4.69%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1154912000</v>
+        <v>-214705920</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.69%</t>
+          <t>0.44%→0.30%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>4609920000</v>
+        <v>434340900</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>5.67%→7.11%</t>
+          <t>0.33%→0.40%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,44 +1230,44 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>434340900</v>
+        <v>4609920000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>5.67%→7.11%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1234800000</v>
+        <v>-272273400</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.54%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→65</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-272273400</v>
+        <v>-441441000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-441441000</v>
+        <v>-1234800000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>1.97%→1.54%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>77→65</t>
         </is>
       </c>
     </row>
@@ -2121,23 +2121,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1154912000</v>
+        <v>-214705920</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.69%</t>
+          <t>0.44%→0.30%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-214705920</v>
+        <v>-1154912000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.30%</t>
+          <t>5.40%→4.69%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2558,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-2186880000</v>
+        <v>-837165000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.95%→0.00%</t>
+          <t>0.80%→0.39%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>102→0</t>
+          <t>203→101</t>
         </is>
       </c>
     </row>
@@ -2586,23 +2586,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>에임드바이오</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-837165000</v>
+        <v>-2186880000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.39%</t>
+          <t>0.95%→0.00%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>203→101</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
@@ -2719,890 +2719,324 @@
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="19" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="19" t="n"/>
+      <c r="I66" s="19" t="n"/>
+      <c r="J66" s="19" t="n"/>
+      <c r="K66" s="19" t="n"/>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>코미코  (신규)</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>395</v>
-      </c>
-      <c r="C69" s="11" t="n">
-        <v>809671000</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→3.03%</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>-56</v>
-      </c>
-      <c r="I69" s="15" t="n">
-        <v>-150220000</v>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
-        <is>
-          <t>8.07%→7.27%</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>780→724</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>65413040</v>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>0.16%→0.40%</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>51→133</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>새로닉스</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-43</v>
-      </c>
-      <c r="I70" s="15" t="n">
-        <v>-34874720</v>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
-        <is>
-          <t>2.97%→2.75%</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>950→907</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
-        <v>69</v>
+        <v>878</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>41154360</v>
+        <v>1619989020</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.28%→0.43%</t>
+          <t>0.00%→3.07%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>122→191</t>
+          <t>0→878</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-34</v>
+        <v>-301</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-23524600</v>
+        <v>-599041170</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.50%</t>
+          <t>2.61%→1.17%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>227→193</t>
+          <t>612→311</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>프로티나  (신규)</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>30800280</v>
+        <v>974715300</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.42%</t>
+          <t>0.00%→1.85%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>474→516</t>
+          <t>0→227</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-24</v>
+        <v>-230</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-84626400</v>
+        <v>-533894400</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.70%</t>
+          <t>2.76%→1.03%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>77→53</t>
+          <t>464→234</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B73" s="11" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>64135800</v>
+        <v>261038700</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>2.94%→3.09%</t>
+          <t>3.57%→3.83%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>321→348</t>
+          <t>498→572</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>리브스메드</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-16</v>
+        <v>-116</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-53161600</v>
+        <v>-453983400</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.31%</t>
+          <t>3.38%→1.73%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
-          <t>121→105</t>
+          <t>349→233</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱  (신규)</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>100936000</v>
+        <v>256627800</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.38%</t>
+          <t>5.63%→6.15%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>0→22</t>
+          <t>256→278</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-11</v>
+        <v>-20</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-43386200</v>
+        <v>-573300000</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.28%</t>
+          <t>3.60%→2.56%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C75" s="11" t="n">
-        <v>20631200</v>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>3.18%→3.17%</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
-        <is>
-          <t>680→697</t>
-        </is>
-      </c>
-      <c r="G75" s="14" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H75" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I75" s="15" t="n">
-        <v>-66748000</v>
-      </c>
-      <c r="J75" s="16" t="inlineStr">
-        <is>
-          <t>2.51%→2.19%</t>
-        </is>
-      </c>
-      <c r="K75" s="13" t="inlineStr">
-        <is>
-          <t>39→35</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>24745600</v>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>5.83%→5.75%</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>977→993</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I76" s="15" t="n">
-        <v>-34254600</v>
-      </c>
-      <c r="J76" s="16" t="inlineStr">
-        <is>
-          <t>1.81%→1.62%</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>41→38</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C77" s="11" t="n">
-        <v>68931000</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>2.55%→2.74%</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>144→159</t>
-        </is>
-      </c>
-      <c r="G77" s="17" t="n"/>
-      <c r="H77" s="17" t="n"/>
-      <c r="I77" s="17" t="n"/>
-      <c r="J77" s="17" t="n"/>
-      <c r="K77" s="17" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C78" s="11" t="n">
-        <v>38694600</v>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>3.04%→3.09%</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>183→192</t>
-        </is>
-      </c>
-      <c r="G78" s="17" t="n"/>
-      <c r="H78" s="17" t="n"/>
-      <c r="I78" s="17" t="n"/>
-      <c r="J78" s="17" t="n"/>
-      <c r="K78" s="17" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C79" s="11" t="n">
-        <v>39775000</v>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>3.13%→3.19%</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G79" s="17" t="n"/>
-      <c r="H79" s="17" t="n"/>
-      <c r="I79" s="17" t="n"/>
-      <c r="J79" s="17" t="n"/>
-      <c r="K79" s="17" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C80" s="11" t="n">
-        <v>6941200</v>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>2.43%→2.38%</t>
-        </is>
-      </c>
-      <c r="E80" s="13" t="inlineStr">
-        <is>
-          <t>363→367</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="n"/>
-      <c r="H80" s="17" t="n"/>
-      <c r="I80" s="17" t="n"/>
-      <c r="J80" s="17" t="n"/>
-      <c r="K80" s="17" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>보로노이  (신규)</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C81" s="11" t="n">
-        <v>22510800</v>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.08%</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>0→2</t>
-        </is>
-      </c>
-      <c r="G81" s="17" t="n"/>
-      <c r="H81" s="17" t="n"/>
-      <c r="I81" s="17" t="n"/>
-      <c r="J81" s="17" t="n"/>
-      <c r="K81" s="17" t="n"/>
-    </row>
-    <row r="83" ht="19" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n"/>
-      <c r="K83" s="4" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K85" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="n">
-        <v>878</v>
-      </c>
-      <c r="C86" s="11" t="n">
-        <v>1619989020</v>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→3.07%</t>
-        </is>
-      </c>
-      <c r="E86" s="13" t="inlineStr">
-        <is>
-          <t>0→878</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t>한스바이오메드</t>
-        </is>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>-301</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>-599041170</v>
-      </c>
-      <c r="J86" s="16" t="inlineStr">
-        <is>
-          <t>2.61%→1.17%</t>
-        </is>
-      </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>612→311</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>프로티나  (신규)</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>227</v>
-      </c>
-      <c r="C87" s="11" t="n">
-        <v>974715300</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.85%</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>0→227</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="n">
-        <v>-230</v>
-      </c>
-      <c r="I87" s="15" t="n">
-        <v>-533894400</v>
-      </c>
-      <c r="J87" s="16" t="inlineStr">
-        <is>
-          <t>2.76%→1.03%</t>
-        </is>
-      </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>464→234</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>알지노믹스</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C88" s="11" t="n">
-        <v>261038700</v>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>3.57%→3.83%</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="inlineStr">
-        <is>
-          <t>498→572</t>
-        </is>
-      </c>
-      <c r="G88" s="14" t="inlineStr">
-        <is>
-          <t>리브스메드</t>
-        </is>
-      </c>
-      <c r="H88" s="15" t="n">
-        <v>-116</v>
-      </c>
-      <c r="I88" s="15" t="n">
-        <v>-453983400</v>
-      </c>
-      <c r="J88" s="16" t="inlineStr">
-        <is>
-          <t>3.38%→1.73%</t>
-        </is>
-      </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>349→233</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>에스티팜</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C89" s="11" t="n">
-        <v>256627800</v>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>5.63%→6.15%</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>256→278</t>
-        </is>
-      </c>
-      <c r="G89" s="14" t="inlineStr">
-        <is>
-          <t>휴젤</t>
-        </is>
-      </c>
-      <c r="H89" s="15" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I89" s="15" t="n">
-        <v>-573300000</v>
-      </c>
-      <c r="J89" s="16" t="inlineStr">
-        <is>
-          <t>3.60%→2.56%</t>
-        </is>
-      </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="18" t="inlineStr">
+    <row r="76" ht="19" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B91" s="19" t="n"/>
-      <c r="C91" s="19" t="n"/>
-      <c r="D91" s="19" t="n"/>
-      <c r="E91" s="19" t="n"/>
-      <c r="F91" s="19" t="n"/>
-      <c r="G91" s="19" t="n"/>
-      <c r="H91" s="19" t="n"/>
-      <c r="I91" s="19" t="n"/>
-      <c r="J91" s="19" t="n"/>
-      <c r="K91" s="19" t="n"/>
+      <c r="B76" s="19" t="n"/>
+      <c r="C76" s="19" t="n"/>
+      <c r="D76" s="19" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="19" t="n"/>
+      <c r="G76" s="19" t="n"/>
+      <c r="H76" s="19" t="n"/>
+      <c r="I76" s="19" t="n"/>
+      <c r="J76" s="19" t="n"/>
+      <c r="K76" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A83:K83"/>
+  <mergeCells count="19">
     <mergeCell ref="G43:K43"/>
-    <mergeCell ref="G67:K67"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="G53:K53"/>
     <mergeCell ref="A66:K66"/>
+    <mergeCell ref="G69:K69"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A42:K42"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A76:K76"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="G32:K32"/>
     <mergeCell ref="A52:K52"/>
-    <mergeCell ref="G84:K84"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:K68"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-14 ~ 2026-08-24  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1272770100</v>
+        <v>-2940470400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.28%</t>
+          <t>2.56%→1.67%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>74→36</t>
+          <t>132→94</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-38</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2940470400</v>
+        <v>-1272770100</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.56%→1.67%</t>
+          <t>0.61%→0.28%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>132→94</t>
+          <t>74→36</t>
         </is>
       </c>
     </row>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>434340900</v>
+        <v>4609920000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>5.67%→7.11%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4609920000</v>
+        <v>434340900</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>5.67%→7.11%</t>
+          <t>0.33%→0.40%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1318,23 +1318,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>923321700</v>
+        <v>414892800</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1362,23 +1362,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>414892800</v>
+        <v>923321700</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1511,23 +1511,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-426520500</v>
+        <v>-1306830000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.21%→3.00%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1539,23 +1539,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1306830000</v>
+        <v>-426520500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>3.21%→3.00%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -2121,23 +2121,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-214705920</v>
+        <v>-1154912000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.30%</t>
+          <t>5.40%→4.69%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1154912000</v>
+        <v>-214705920</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.69%</t>
+          <t>0.44%→0.30%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -2237,23 +2237,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-593472000</v>
+        <v>-781440000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>5.13%→5.05%</t>
+          <t>1.35%→0.95%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>110→105</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-781440000</v>
+        <v>-593472000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.35%→0.95%</t>
+          <t>5.13%→5.05%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>110→105</t>
         </is>
       </c>
     </row>
@@ -2719,324 +2719,890 @@
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
-      <c r="J66" s="19" t="n"/>
-      <c r="K66" s="19" t="n"/>
-    </row>
-    <row r="68" ht="19" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.3%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 13종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="8" t="n"/>
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>809671000</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.03%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>0→395</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-150220000</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>8.07%→7.27%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>780→724</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>65413040</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.16%→0.40%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>51→133</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-34874720</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>2.97%→2.75%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
-        <v>878</v>
+        <v>69</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>1619989020</v>
+        <v>41154360</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.07%</t>
+          <t>0.28%→0.43%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>0→878</t>
+          <t>122→191</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-301</v>
+        <v>-34</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-599041170</v>
+        <v>-23524600</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.61%→1.17%</t>
+          <t>0.61%→0.50%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>612→311</t>
+          <t>227→193</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>프로티나  (신규)</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>974715300</v>
+        <v>30800280</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.85%</t>
+          <t>1.34%→1.42%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>0→227</t>
+          <t>474→516</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-230</v>
+        <v>-24</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-533894400</v>
+        <v>-84626400</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.76%→1.03%</t>
+          <t>1.05%→0.70%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>464→234</t>
+          <t>77→53</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B73" s="11" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>261038700</v>
+        <v>64135800</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.83%</t>
+          <t>2.94%→3.09%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>498→572</t>
+          <t>321→348</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>리브스메드</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-116</v>
+        <v>-16</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-453983400</v>
+        <v>-53161600</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>3.38%→1.73%</t>
+          <t>1.55%→1.31%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
-          <t>349→233</t>
+          <t>121→105</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>오름테라퓨틱  (신규)</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C74" s="11" t="n">
+        <v>100936000</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.38%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-43386200</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.28%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>20631200</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>3.18%→3.17%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>680→697</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-66748000</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>2.51%→2.19%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>39→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>24745600</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>5.83%→5.75%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>977→993</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-34254600</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>1.81%→1.62%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>68931000</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>2.55%→2.74%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>144→159</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n"/>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="n"/>
+      <c r="K77" s="17" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>38694600</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.04%→3.09%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n"/>
+      <c r="H78" s="17" t="n"/>
+      <c r="I78" s="17" t="n"/>
+      <c r="J78" s="17" t="n"/>
+      <c r="K78" s="17" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>39775000</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.19%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>6941200</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>2.43%→2.38%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>363→367</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="n"/>
+      <c r="H80" s="17" t="n"/>
+      <c r="I80" s="17" t="n"/>
+      <c r="J80" s="17" t="n"/>
+      <c r="K80" s="17" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>보로노이  (신규)</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>22510800</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.08%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>0→2</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n"/>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-24  vs  5일전 2026-08-14      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>878</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>1619989020</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.07%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>0→878</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>-301</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>-599041170</v>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>2.61%→1.17%</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>612→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>974715300</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.85%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>-533894400</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→1.03%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>261038700</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>3.57%→3.83%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>-453983400</v>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>3.38%→1.73%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C89" s="11" t="n">
         <v>256627800</v>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>5.63%→6.15%</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>256→278</t>
         </is>
       </c>
-      <c r="G74" s="14" t="inlineStr">
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n">
+      <c r="H89" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I74" s="15" t="n">
+      <c r="I89" s="15" t="n">
         <v>-573300000</v>
       </c>
-      <c r="J74" s="16" t="inlineStr">
+      <c r="J89" s="16" t="inlineStr">
         <is>
           <t>3.60%→2.56%</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="19" customHeight="1">
-      <c r="A76" s="18" t="inlineStr">
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B76" s="19" t="n"/>
-      <c r="C76" s="19" t="n"/>
-      <c r="D76" s="19" t="n"/>
-      <c r="E76" s="19" t="n"/>
-      <c r="F76" s="19" t="n"/>
-      <c r="G76" s="19" t="n"/>
-      <c r="H76" s="19" t="n"/>
-      <c r="I76" s="19" t="n"/>
-      <c r="J76" s="19" t="n"/>
-      <c r="K76" s="19" t="n"/>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="19" t="n"/>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="19" t="n"/>
+      <c r="G91" s="19" t="n"/>
+      <c r="H91" s="19" t="n"/>
+      <c r="I91" s="19" t="n"/>
+      <c r="J91" s="19" t="n"/>
+      <c r="K91" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="21">
+    <mergeCell ref="A83:K83"/>
     <mergeCell ref="G43:K43"/>
+    <mergeCell ref="G67:K67"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="G53:K53"/>
     <mergeCell ref="A66:K66"/>
-    <mergeCell ref="G69:K69"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A42:K42"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A76:K76"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="G32:K32"/>
     <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="G84:K84"/>
+    <mergeCell ref="A67:E67"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260824.xlsx
+++ b/reports/pdf_rolling5_20260824.xlsx
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-272273400</v>
+        <v>-441441000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.57%→1.36%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1295,46 +1295,46 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-441441000</v>
+        <v>-272273400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.57%→1.36%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>414892800</v>
+        <v>923321700</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.39%</t>
+          <t>1.20%→1.39%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1362,23 +1362,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>923321700</v>
+        <v>414892800</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.39%</t>
+          <t>1.41%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1511,23 +1511,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1306830000</v>
+        <v>-426520500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.21%→3.00%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1539,23 +1539,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-426520500</v>
+        <v>-1306830000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.21%→3.00%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -2056,23 +2056,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1282688000</v>
+        <v>1214400000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.62%</t>
+          <t>1.27%→1.72%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>20→120</t>
+          <t>250→350</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -2100,44 +2100,44 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1214400000</v>
+        <v>1282688000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.72%</t>
+          <t>0.09%→0.62%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>250→350</t>
+          <t>20→120</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1154912000</v>
+        <v>-214705920</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.69%</t>
+          <t>0.44%→0.30%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-214705920</v>
+        <v>-1154912000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.30%</t>
+          <t>5.40%→4.69%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2558,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>에임드바이오</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-837165000</v>
+        <v>-2186880000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.39%</t>
+          <t>0.95%→0.00%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>203→101</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
@@ -2586,23 +2586,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-2186880000</v>
+        <v>-837165000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.95%→0.00%</t>
+          <t>0.80%→0.39%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>102→0</t>
+          <t>203→101</t>
         </is>
       </c>
     </row>
